--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/TENNESSEE_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/TENNESSEE_2010.xlsx
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C106">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C165">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C566">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C629">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C648">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C892">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1018">
